--- a/datos.xlsx
+++ b/datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pci\Documents\GitHub\Imagen-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ECDC141F-81E8-4EC4-829D-D1B7467AFB42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02564BCF-945F-44EE-B1B5-581F553C5613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E4000D76-12C8-4C65-B235-B01DAADFA291}"/>
   </bookViews>
@@ -39,18 +39,6 @@
     <t>Folio</t>
   </si>
   <si>
-    <t>Caja -Caseta: TIPO</t>
-  </si>
-  <si>
-    <t>Caja -Caseta: ESTADO</t>
-  </si>
-  <si>
-    <t>Caja -Caseta: AREA</t>
-  </si>
-  <si>
-    <t>Caja -Caseta: DISTRITO TELEFONO</t>
-  </si>
-  <si>
     <t>Registro Existe ?</t>
   </si>
   <si>
@@ -124,6 +112,18 @@
   </si>
   <si>
     <t>12365180-1259_despues.jpg</t>
+  </si>
+  <si>
+    <t>DISTRITO TELEFONO</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>Area</t>
   </si>
 </sst>
 </file>
@@ -483,176 +483,176 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
